--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/Qwen3-4B-Instruct-2507/metrics_default_vs_aae.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/Qwen3-4B-Instruct-2507/metrics_default_vs_aae.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.7362637362637363</v>
+        <v>0.8448275862068966</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.7112676056338029</v>
+        <v>0.7816901408450704</v>
       </c>
       <c r="D2">
-        <v>0.3796296296296297</v>
+        <v>0.2403100775193799</v>
       </c>
       <c r="E2">
-        <v>91</v>
+        <v>116</v>
       </c>
       <c r="F2">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="G2">
-        <v>34</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/Qwen3-4B-Instruct-2507/metrics_default_vs_aae.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/Qwen3-4B-Instruct-2507/metrics_default_vs_aae.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.8448275862068966</v>
+        <v>0.8376068376068376</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.7816901408450704</v>
+        <v>0.7746478873239436</v>
       </c>
       <c r="D2">
-        <v>0.2403100775193799</v>
+        <v>0.2461538461538462</v>
       </c>
       <c r="E2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F2">
         <v>13</v>
       </c>
       <c r="G2">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
